--- a/artfynd/A 36581-2026 artfynd.xlsx
+++ b/artfynd/A 36581-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137228383</v>
       </c>
       <c r="B2" t="n">
-        <v>96692</v>
+        <v>96694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137229948</v>
       </c>
       <c r="B3" t="n">
-        <v>92200</v>
+        <v>92202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,53 +884,61 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137233918</v>
+        <v>137249167</v>
       </c>
       <c r="B4" t="n">
-        <v>101599</v>
+        <v>58036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stärkerstorp S 520 m, Ög</t>
+          <t>Norr om Kryddviken, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566937</v>
+        <v>566914</v>
       </c>
       <c r="R4" t="n">
-        <v>6510991</v>
+        <v>6511023</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,39 +973,154 @@
           <t>2026-10-13</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökande högt upp i en björk.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Granskog med inslag av asp</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan-Erik Axelsson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan-Erik Axelsson, Mirjam Ideström, Eva Siljeholm, Anette Källman</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137249167</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137233918</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101601</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stärkerstorp S 520 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>566937</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6510991</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Granskog med inslag av asp</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan-Erik Axelsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan-Erik Axelsson, Mirjam Ideström, Eva Siljeholm, Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137233918</t>
         </is>
@@ -1008,6 +1131,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36581-2026 artfynd.xlsx
+++ b/artfynd/A 36581-2026 artfynd.xlsx
@@ -914,16 +914,8 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1037,11 +1029,7 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">

--- a/artfynd/A 36581-2026 artfynd.xlsx
+++ b/artfynd/A 36581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137228383</v>
       </c>
       <c r="B2" t="n">
-        <v>96694</v>
+        <v>96697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137229948</v>
       </c>
       <c r="B3" t="n">
-        <v>92202</v>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137233918</v>
       </c>
       <c r="B5" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36581-2026 artfynd.xlsx
+++ b/artfynd/A 36581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137228383</v>
       </c>
       <c r="B2" t="n">
-        <v>96697</v>
+        <v>96707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137229948</v>
       </c>
       <c r="B3" t="n">
-        <v>92205</v>
+        <v>92215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137249167</v>
       </c>
       <c r="B4" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137233918</v>
       </c>
       <c r="B5" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36581-2026 artfynd.xlsx
+++ b/artfynd/A 36581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137228383</v>
       </c>
       <c r="B2" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137229948</v>
       </c>
       <c r="B3" t="n">
-        <v>92215</v>
+        <v>92216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137233918</v>
       </c>
       <c r="B5" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36581-2026 artfynd.xlsx
+++ b/artfynd/A 36581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137228383</v>
       </c>
       <c r="B2" t="n">
-        <v>96708</v>
+        <v>96713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137229948</v>
       </c>
       <c r="B3" t="n">
-        <v>92216</v>
+        <v>92219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137249167</v>
       </c>
       <c r="B4" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137233918</v>
       </c>
       <c r="B5" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36581-2026 artfynd.xlsx
+++ b/artfynd/A 36581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137228383</v>
       </c>
       <c r="B2" t="n">
-        <v>96713</v>
+        <v>96715</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137229948</v>
       </c>
       <c r="B3" t="n">
-        <v>92219</v>
+        <v>92221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137233918</v>
       </c>
       <c r="B5" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36581-2026 artfynd.xlsx
+++ b/artfynd/A 36581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137228383</v>
       </c>
       <c r="B2" t="n">
-        <v>96715</v>
+        <v>96721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137229948</v>
       </c>
       <c r="B3" t="n">
-        <v>92221</v>
+        <v>92226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137249167</v>
       </c>
       <c r="B4" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137233918</v>
       </c>
       <c r="B5" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36581-2026 artfynd.xlsx
+++ b/artfynd/A 36581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137228383</v>
       </c>
       <c r="B2" t="n">
-        <v>96721</v>
+        <v>96733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137229948</v>
       </c>
       <c r="B3" t="n">
-        <v>92226</v>
+        <v>92238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137233918</v>
       </c>
       <c r="B5" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36581-2026 artfynd.xlsx
+++ b/artfynd/A 36581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137228383</v>
       </c>
       <c r="B2" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137229948</v>
       </c>
       <c r="B3" t="n">
-        <v>92238</v>
+        <v>92239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137233918</v>
       </c>
       <c r="B5" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36581-2026 artfynd.xlsx
+++ b/artfynd/A 36581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137228383</v>
       </c>
       <c r="B2" t="n">
-        <v>96734</v>
+        <v>96737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137229948</v>
       </c>
       <c r="B3" t="n">
-        <v>92239</v>
+        <v>92242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137233918</v>
       </c>
       <c r="B5" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36581-2026 artfynd.xlsx
+++ b/artfynd/A 36581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137228383</v>
       </c>
       <c r="B2" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137229948</v>
       </c>
       <c r="B3" t="n">
-        <v>92242</v>
+        <v>92246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137249167</v>
       </c>
       <c r="B4" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137233918</v>
       </c>
       <c r="B5" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
